--- a/docs/mutual information after cleaning.xlsx
+++ b/docs/mutual information after cleaning.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kushn\projects\kaggle\Telco customer churn 11.1.3\telco-customer-churn\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68D26DEE-35CA-47B4-B8D2-A97B3BF1FC5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B5E9202-2AB0-4E7B-82EC-9438244EE19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1710" windowWidth="29040" windowHeight="15720" xr2:uid="{EF238555-2496-4093-8BBF-7018B023DB21}"/>
+    <workbookView xWindow="-14685" yWindow="2385" windowWidth="13650" windowHeight="15345" activeTab="2" xr2:uid="{EF238555-2496-4093-8BBF-7018B023DB21}"/>
+    <workbookView xWindow="-28920" yWindow="1710" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{99A4C60C-90BA-48B8-87B6-754AB4E2835B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="158">
   <si>
     <t>Feature</t>
   </si>
@@ -183,14 +186,345 @@
   </si>
   <si>
     <t>Gender_Female</t>
+  </si>
+  <si>
+    <t>TechSupport-OnlineSecurity-combined</t>
+  </si>
+  <si>
+    <t>Dependents-Partner-combined</t>
+  </si>
+  <si>
+    <t>PhoneService-PaperlessBilling-combined</t>
+  </si>
+  <si>
+    <t>Dependents-OnlineSecurity-combined</t>
+  </si>
+  <si>
+    <t>Partner-Dependents-combined</t>
+  </si>
+  <si>
+    <t>TechSupport-DeviceProtection-combined</t>
+  </si>
+  <si>
+    <t>OnlineBackup-TechSupport-combined</t>
+  </si>
+  <si>
+    <t>OnlineSecurity-StreamingMovies-combined</t>
+  </si>
+  <si>
+    <t>StreamingMovies-OnlineBackup-combined</t>
+  </si>
+  <si>
+    <t>DeviceProtection-TechSupport-combined</t>
+  </si>
+  <si>
+    <t>DeviceProtection-Dependents-combined</t>
+  </si>
+  <si>
+    <t>Partner-OnlineSecurity-combined</t>
+  </si>
+  <si>
+    <t>OnlineSecurity-OnlineBackup-combined</t>
+  </si>
+  <si>
+    <t>PaperlessBilling-PhoneService-combined</t>
+  </si>
+  <si>
+    <t>TechSupport-Dependents-combined</t>
+  </si>
+  <si>
+    <t>TechSupport-OnlineBackup-combined</t>
+  </si>
+  <si>
+    <t>OnlineSecurity-Partner-combined</t>
+  </si>
+  <si>
+    <t>Dependents-TechSupport-combined</t>
+  </si>
+  <si>
+    <t>PhoneService-Partner-combined</t>
+  </si>
+  <si>
+    <t>Partner-PhoneService-combined</t>
+  </si>
+  <si>
+    <t>OnlineSecurity-DeviceProtection-combined</t>
+  </si>
+  <si>
+    <t>Dependents-StreamingTV-combined</t>
+  </si>
+  <si>
+    <t>PhoneService-OnlineSecurity-combined</t>
+  </si>
+  <si>
+    <t>PhoneService-Dependents-combined</t>
+  </si>
+  <si>
+    <t>SeniorCitizen-PaperlessBilling-combined</t>
+  </si>
+  <si>
+    <t>OnlineSecurity-PhoneService-combined</t>
+  </si>
+  <si>
+    <t>Partner-TechSupport-combined</t>
+  </si>
+  <si>
+    <t>PaperlessBilling-StreamingTV-combined</t>
+  </si>
+  <si>
+    <t>StreamingMovies-PaperlessBilling-combined</t>
+  </si>
+  <si>
+    <t>StreamingTV-PhoneService-combined</t>
+  </si>
+  <si>
+    <t>StreamingMovies-OnlineSecurity-combined</t>
+  </si>
+  <si>
+    <t>OnlineBackup-DeviceProtection-combined</t>
+  </si>
+  <si>
+    <t>PhoneService-TechSupport-combined</t>
+  </si>
+  <si>
+    <t>StreamingMovies-PhoneService-combined</t>
+  </si>
+  <si>
+    <t>PaperlessBilling-StreamingMovies-combined</t>
+  </si>
+  <si>
+    <t>TechSupport-Partner-combined</t>
+  </si>
+  <si>
+    <t>SeniorCitizen-Dependents-combined</t>
+  </si>
+  <si>
+    <t>PaperlessBilling-OnlineSecurity-combined</t>
+  </si>
+  <si>
+    <t>TechSupport-StreamingTV-combined</t>
+  </si>
+  <si>
+    <t>TechSupport-PhoneService-combined</t>
+  </si>
+  <si>
+    <t>DeviceProtection-StreamingTV-combined</t>
+  </si>
+  <si>
+    <t>DeviceProtection-OnlineSecurity-combined</t>
+  </si>
+  <si>
+    <t>StreamingMovies-SeniorCitizen-combined</t>
+  </si>
+  <si>
+    <t>Dependents-DeviceProtection-combined</t>
+  </si>
+  <si>
+    <t>OnlineSecurity-TechSupport-combined</t>
+  </si>
+  <si>
+    <t>StreamingTV-DeviceProtection-combined</t>
+  </si>
+  <si>
+    <t>PaperlessBilling-DeviceProtection-combined</t>
+  </si>
+  <si>
+    <t>SeniorCitizen-OnlineSecurity-combined</t>
+  </si>
+  <si>
+    <t>TechSupport-SeniorCitizen-combined</t>
+  </si>
+  <si>
+    <t>StreamingMovies-Dependents-combined</t>
+  </si>
+  <si>
+    <t>StreamingTV-OnlineSecurity-combined</t>
+  </si>
+  <si>
+    <t>OnlineSecurity-SeniorCitizen-combined</t>
+  </si>
+  <si>
+    <t>OnlineBackup-Partner-combined</t>
+  </si>
+  <si>
+    <t>DeviceProtection-PaperlessBilling-combined</t>
+  </si>
+  <si>
+    <t>OnlineBackup-PhoneService-combined</t>
+  </si>
+  <si>
+    <t>PaperlessBilling-OnlineBackup-combined</t>
+  </si>
+  <si>
+    <t>SeniorCitizen-OnlineBackup-combined</t>
+  </si>
+  <si>
+    <t>OnlineBackup-Dependents-combined</t>
+  </si>
+  <si>
+    <t>Dependents-PhoneService-combined</t>
+  </si>
+  <si>
+    <t>Partner-OnlineBackup-combined</t>
+  </si>
+  <si>
+    <t>StreamingTV-TechSupport-combined</t>
+  </si>
+  <si>
+    <t>OnlineBackup-SeniorCitizen-combined</t>
+  </si>
+  <si>
+    <t>Partner-StreamingTV-combined</t>
+  </si>
+  <si>
+    <t>Partner-PaperlessBilling-combined</t>
+  </si>
+  <si>
+    <t>PhoneService-StreamingTV-combined</t>
+  </si>
+  <si>
+    <t>StreamingMovies-TechSupport-combined</t>
+  </si>
+  <si>
+    <t>Dependents-StreamingMovies-combined</t>
+  </si>
+  <si>
+    <t>Dependents-OnlineBackup-combined</t>
+  </si>
+  <si>
+    <t>PhoneService-OnlineBackup-combined</t>
+  </si>
+  <si>
+    <t>PhoneService-SeniorCitizen-combined</t>
+  </si>
+  <si>
+    <t>TechSupport-StreamingMovies-combined</t>
+  </si>
+  <si>
+    <t>StreamingMovies-StreamingTV-combined</t>
+  </si>
+  <si>
+    <t>OnlineSecurity-Dependents-combined</t>
+  </si>
+  <si>
+    <t>TechSupport-PaperlessBilling-combined</t>
+  </si>
+  <si>
+    <t>StreamingMovies-DeviceProtection-combined</t>
+  </si>
+  <si>
+    <t>StreamingTV-PaperlessBilling-combined</t>
+  </si>
+  <si>
+    <t>PaperlessBilling-TechSupport-combined</t>
+  </si>
+  <si>
+    <t>Partner-StreamingMovies-combined</t>
+  </si>
+  <si>
+    <t>Partner-DeviceProtection-combined</t>
+  </si>
+  <si>
+    <t>OnlineSecurity-StreamingTV-combined</t>
+  </si>
+  <si>
+    <t>DeviceProtection-StreamingMovies-combined</t>
+  </si>
+  <si>
+    <t>DeviceProtection-PhoneService-combined</t>
+  </si>
+  <si>
+    <t>StreamingMovies-Partner-combined</t>
+  </si>
+  <si>
+    <t>PaperlessBilling-SeniorCitizen-combined</t>
+  </si>
+  <si>
+    <t>StreamingTV-OnlineBackup-combined</t>
+  </si>
+  <si>
+    <t>PhoneService-StreamingMovies-combined</t>
+  </si>
+  <si>
+    <t>PhoneService-DeviceProtection-combined</t>
+  </si>
+  <si>
+    <t>StreamingTV-StreamingMovies-combined</t>
+  </si>
+  <si>
+    <t>SeniorCitizen-Partner-combined</t>
+  </si>
+  <si>
+    <t>PaperlessBilling-Dependents-combined</t>
+  </si>
+  <si>
+    <t>SeniorCitizen-PhoneService-combined</t>
+  </si>
+  <si>
+    <t>Dependents-PaperlessBilling-combined</t>
+  </si>
+  <si>
+    <t>Dependents-SeniorCitizen-combined</t>
+  </si>
+  <si>
+    <t>SeniorCitizen-DeviceProtection-combined</t>
+  </si>
+  <si>
+    <t>Partner-SeniorCitizen-combined</t>
+  </si>
+  <si>
+    <t>SeniorCitizen-StreamingMovies-combined</t>
+  </si>
+  <si>
+    <t>PaperlessBilling-Partner-combined</t>
+  </si>
+  <si>
+    <t>StreamingTV-Dependents-combined</t>
+  </si>
+  <si>
+    <t>DeviceProtection-OnlineBackup-combined</t>
+  </si>
+  <si>
+    <t>StreamingTV-Partner-combined</t>
+  </si>
+  <si>
+    <t>StreamingTV-SeniorCitizen-combined</t>
+  </si>
+  <si>
+    <t>OnlineSecurity-PaperlessBilling-combined</t>
+  </si>
+  <si>
+    <t>SeniorCitizen-StreamingTV-combined</t>
+  </si>
+  <si>
+    <t>OnlineBackup-PaperlessBilling-combined</t>
+  </si>
+  <si>
+    <t>OnlineBackup-OnlineSecurity-combined</t>
+  </si>
+  <si>
+    <t>OnlineBackup-StreamingTV-combined</t>
+  </si>
+  <si>
+    <t>OnlineBackup-StreamingMovies-combined</t>
+  </si>
+  <si>
+    <t>DeviceProtection-SeniorCitizen-combined</t>
+  </si>
+  <si>
+    <t>DeviceProtection-Partner-combined</t>
+  </si>
+  <si>
+    <t>SeniorCitizen-TechSupport-combined</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.00000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -201,7 +535,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -322,6 +656,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -335,7 +675,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -357,6 +697,10 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1405,4 +1749,2853 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8887B92A-3603-4DD7-8BB9-21BE27929059}">
+  <dimension ref="A2:F157"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="39.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.73046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.73046875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="21">
+        <v>9.5200000000000007E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="21">
+        <v>7.7899999999999997E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="21">
+        <v>6.6699999999999995E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="21">
+        <v>6.2700000000000006E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="21">
+        <v>5.9900000000000002E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="21">
+        <v>5.1900000000000002E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="21">
+        <v>4.65E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="21">
+        <v>4.3400000000000001E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="21">
+        <v>4.2599999999999999E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="21">
+        <v>4.2200000000000001E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="21">
+        <v>4.1399999999999999E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="21">
+        <v>3.6299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="21">
+        <v>3.6200000000000003E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="21">
+        <v>3.3799999999999997E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="21">
+        <v>3.2000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="21">
+        <v>3.1E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="21">
+        <v>3.0499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="22">
+        <v>2.7799999999999998E-2</v>
+      </c>
+      <c r="C19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="21">
+        <v>1.77E-2</v>
+      </c>
+      <c r="E19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="21">
+        <v>1.8499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="21">
+        <v>2.7099999999999999E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="21">
+        <v>2.3599999999999999E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A22" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="22">
+        <v>2.2800000000000001E-2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="21">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="E22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="21">
+        <v>2.12E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="21">
+        <v>2.12E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="21">
+        <v>2.06E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="21">
+        <v>2.0500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="21">
+        <v>2.0400000000000001E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="21">
+        <v>2.0199999999999999E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A28" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="22">
+        <v>1.9699999999999999E-2</v>
+      </c>
+      <c r="C28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" s="21">
+        <v>1.4E-2</v>
+      </c>
+      <c r="E28" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" s="21">
+        <v>1.8499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" s="21">
+        <v>1.8499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30" s="21">
+        <v>1.77E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A31" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="22">
+        <v>1.7299999999999999E-2</v>
+      </c>
+      <c r="C31" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="21">
+        <v>0.01</v>
+      </c>
+      <c r="E31" t="s">
+        <v>26</v>
+      </c>
+      <c r="F31" s="21">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A32" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="24">
+        <v>1.7100000000000001E-2</v>
+      </c>
+      <c r="C32" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" s="21">
+        <v>1.77E-2</v>
+      </c>
+      <c r="E32" t="s">
+        <v>45</v>
+      </c>
+      <c r="F32" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A33" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="24">
+        <v>1.66E-2</v>
+      </c>
+      <c r="C33" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" s="21">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="E33" t="s">
+        <v>21</v>
+      </c>
+      <c r="F33" s="21">
+        <v>1.77E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A34" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" s="24">
+        <v>1.5800000000000002E-2</v>
+      </c>
+      <c r="C34" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" s="21">
+        <v>1.8499999999999999E-2</v>
+      </c>
+      <c r="E34" t="s">
+        <v>38</v>
+      </c>
+      <c r="F34" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A35" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B35" s="22">
+        <v>1.5699999999999999E-2</v>
+      </c>
+      <c r="C35" t="s">
+        <v>38</v>
+      </c>
+      <c r="D35" s="21">
+        <v>0</v>
+      </c>
+      <c r="E35" t="s">
+        <v>40</v>
+      </c>
+      <c r="F35" s="21">
+        <v>2.3999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="21">
+        <v>1.5699999999999999E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A37" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="22">
+        <v>1.47E-2</v>
+      </c>
+      <c r="C37" t="s">
+        <v>45</v>
+      </c>
+      <c r="D37" s="21">
+        <v>0</v>
+      </c>
+      <c r="E37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F37" s="21">
+        <v>1.77E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A38" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" s="22">
+        <v>1.47E-2</v>
+      </c>
+      <c r="C38" t="s">
+        <v>45</v>
+      </c>
+      <c r="D38" s="21">
+        <v>0</v>
+      </c>
+      <c r="E38" t="s">
+        <v>26</v>
+      </c>
+      <c r="F38" s="21">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A39" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39" s="24">
+        <v>1.46E-2</v>
+      </c>
+      <c r="C39" t="s">
+        <v>30</v>
+      </c>
+      <c r="D39" s="21">
+        <v>0.01</v>
+      </c>
+      <c r="E39" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="21">
+        <v>1.8499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A40" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="B40" s="24">
+        <v>1.4E-2</v>
+      </c>
+      <c r="C40" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" s="21">
+        <v>1.8499999999999999E-2</v>
+      </c>
+      <c r="E40" t="s">
+        <v>40</v>
+      </c>
+      <c r="F40" s="21">
+        <v>2.3999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>26</v>
+      </c>
+      <c r="B41" s="21">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A42" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B42" s="24">
+        <v>1.3299999999999999E-2</v>
+      </c>
+      <c r="C42" t="s">
+        <v>25</v>
+      </c>
+      <c r="D42" s="21">
+        <v>2.12E-2</v>
+      </c>
+      <c r="E42" t="s">
+        <v>27</v>
+      </c>
+      <c r="F42" s="21">
+        <v>6.8999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>62</v>
+      </c>
+      <c r="B43" s="21">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A44" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="B44" s="24">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="C44" t="s">
+        <v>21</v>
+      </c>
+      <c r="D44" s="21">
+        <v>1.77E-2</v>
+      </c>
+      <c r="E44" t="s">
+        <v>40</v>
+      </c>
+      <c r="F44" s="21">
+        <v>2.3999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>23</v>
+      </c>
+      <c r="B45" s="21">
+        <v>1.2800000000000001E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A46" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="B46" s="24">
+        <v>1.26E-2</v>
+      </c>
+      <c r="C46" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" s="21">
+        <v>1.8499999999999999E-2</v>
+      </c>
+      <c r="E46" t="s">
+        <v>30</v>
+      </c>
+      <c r="F46" s="21">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A47" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="B47" s="24">
+        <v>1.2200000000000001E-2</v>
+      </c>
+      <c r="C47" t="s">
+        <v>26</v>
+      </c>
+      <c r="D47" s="21">
+        <v>1.4E-2</v>
+      </c>
+      <c r="E47" t="s">
+        <v>21</v>
+      </c>
+      <c r="F47" s="21">
+        <v>1.77E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A48" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B48" s="22">
+        <v>1.21E-2</v>
+      </c>
+      <c r="C48" t="s">
+        <v>27</v>
+      </c>
+      <c r="D48" s="21">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="E48" t="s">
+        <v>30</v>
+      </c>
+      <c r="F48" s="21">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>32</v>
+      </c>
+      <c r="B49" s="21">
+        <v>1.17E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A50" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B50" s="22">
+        <v>1.14E-2</v>
+      </c>
+      <c r="C50" t="s">
+        <v>30</v>
+      </c>
+      <c r="D50" s="21">
+        <v>0.01</v>
+      </c>
+      <c r="E50" t="s">
+        <v>27</v>
+      </c>
+      <c r="F50" s="21">
+        <v>6.8999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A51" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="B51" s="24">
+        <v>1.11E-2</v>
+      </c>
+      <c r="C51" t="s">
+        <v>22</v>
+      </c>
+      <c r="D51" s="21">
+        <v>1.8499999999999999E-2</v>
+      </c>
+      <c r="E51" t="s">
+        <v>45</v>
+      </c>
+      <c r="F51" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A52" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52" s="24">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="C52" t="s">
+        <v>26</v>
+      </c>
+      <c r="D52" s="21">
+        <v>1.4E-2</v>
+      </c>
+      <c r="E52" t="s">
+        <v>35</v>
+      </c>
+      <c r="F52" s="21">
+        <v>4.8999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A53" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="B53" s="24">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="C53" t="s">
+        <v>27</v>
+      </c>
+      <c r="D53" s="21">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="E53" t="s">
+        <v>22</v>
+      </c>
+      <c r="F53" s="21">
+        <v>1.8499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A54" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="B54" s="24">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="C54" t="s">
+        <v>27</v>
+      </c>
+      <c r="D54" s="21">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="E54" t="s">
+        <v>26</v>
+      </c>
+      <c r="F54" s="21">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A55" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="B55" s="24">
+        <v>1.0500000000000001E-2</v>
+      </c>
+      <c r="C55" t="s">
+        <v>31</v>
+      </c>
+      <c r="D55" s="21">
+        <v>8.2000000000000007E-3</v>
+      </c>
+      <c r="E55" t="s">
+        <v>25</v>
+      </c>
+      <c r="F55" s="21">
+        <v>2.12E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A56" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="B56" s="24">
+        <v>1.03E-2</v>
+      </c>
+      <c r="C56" t="s">
+        <v>22</v>
+      </c>
+      <c r="D56" s="21">
+        <v>1.8499999999999999E-2</v>
+      </c>
+      <c r="E56" t="s">
+        <v>27</v>
+      </c>
+      <c r="F56" s="21">
+        <v>6.8999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>30</v>
+      </c>
+      <c r="B57" s="21">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>74</v>
+      </c>
+      <c r="B58" s="21">
+        <v>9.7000000000000003E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>75</v>
+      </c>
+      <c r="B59" s="21">
+        <v>9.7000000000000003E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>76</v>
+      </c>
+      <c r="B60" s="21">
+        <v>9.5999999999999992E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>77</v>
+      </c>
+      <c r="B61" s="21">
+        <v>9.4000000000000004E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>78</v>
+      </c>
+      <c r="B62" s="21">
+        <v>9.4000000000000004E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>79</v>
+      </c>
+      <c r="B63" s="21">
+        <v>8.8999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>80</v>
+      </c>
+      <c r="B64" s="21">
+        <v>8.8000000000000005E-3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>81</v>
+      </c>
+      <c r="B65" s="21">
+        <v>8.5000000000000006E-3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>82</v>
+      </c>
+      <c r="B66" s="21">
+        <v>8.5000000000000006E-3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>83</v>
+      </c>
+      <c r="B67" s="21">
+        <v>8.3000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>84</v>
+      </c>
+      <c r="B68" s="21">
+        <v>8.3000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>31</v>
+      </c>
+      <c r="B69" s="21">
+        <v>8.2000000000000007E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>85</v>
+      </c>
+      <c r="B70" s="21">
+        <v>8.0999999999999996E-3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>86</v>
+      </c>
+      <c r="B71" s="21">
+        <v>7.7999999999999996E-3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A72" t="s">
+        <v>87</v>
+      </c>
+      <c r="B72" s="21">
+        <v>7.7000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>36</v>
+      </c>
+      <c r="B73" s="21">
+        <v>7.6E-3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>28</v>
+      </c>
+      <c r="B74" s="21">
+        <v>7.6E-3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
+        <v>88</v>
+      </c>
+      <c r="B75" s="21">
+        <v>7.3000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A76" t="s">
+        <v>27</v>
+      </c>
+      <c r="B76" s="21">
+        <v>6.8999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A77" t="s">
+        <v>89</v>
+      </c>
+      <c r="B77" s="21">
+        <v>6.7000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A78" t="s">
+        <v>90</v>
+      </c>
+      <c r="B78" s="21">
+        <v>6.3E-3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A79" t="s">
+        <v>91</v>
+      </c>
+      <c r="B79" s="21">
+        <v>6.1999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A80" t="s">
+        <v>92</v>
+      </c>
+      <c r="B80" s="21">
+        <v>6.1999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A81" t="s">
+        <v>93</v>
+      </c>
+      <c r="B81" s="21">
+        <v>5.7999999999999996E-3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A82" t="s">
+        <v>94</v>
+      </c>
+      <c r="B82" s="21">
+        <v>5.5999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A83" t="s">
+        <v>47</v>
+      </c>
+      <c r="B83" s="21">
+        <v>5.4999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A84" t="s">
+        <v>95</v>
+      </c>
+      <c r="B84" s="21">
+        <v>5.4999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A85" t="s">
+        <v>34</v>
+      </c>
+      <c r="B85" s="21">
+        <v>5.4999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A86" t="s">
+        <v>96</v>
+      </c>
+      <c r="B86" s="21">
+        <v>5.1999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A87" t="s">
+        <v>33</v>
+      </c>
+      <c r="B87" s="21">
+        <v>5.1000000000000004E-3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A88" t="s">
+        <v>35</v>
+      </c>
+      <c r="B88" s="21">
+        <v>4.8999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A89" t="s">
+        <v>97</v>
+      </c>
+      <c r="B89" s="21">
+        <v>4.8999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A90" t="s">
+        <v>98</v>
+      </c>
+      <c r="B90" s="21">
+        <v>4.7999999999999996E-3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A91" t="s">
+        <v>99</v>
+      </c>
+      <c r="B91" s="21">
+        <v>4.5999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A92" t="s">
+        <v>100</v>
+      </c>
+      <c r="B92" s="21">
+        <v>4.3E-3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A93" t="s">
+        <v>101</v>
+      </c>
+      <c r="B93" s="21">
+        <v>3.8999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A94" t="s">
+        <v>102</v>
+      </c>
+      <c r="B94" s="21">
+        <v>3.8999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A95" t="s">
+        <v>103</v>
+      </c>
+      <c r="B95" s="21">
+        <v>3.8E-3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A96" t="s">
+        <v>104</v>
+      </c>
+      <c r="B96" s="21">
+        <v>3.5000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A97" t="s">
+        <v>105</v>
+      </c>
+      <c r="B97" s="21">
+        <v>3.3E-3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A98" t="s">
+        <v>106</v>
+      </c>
+      <c r="B98" s="21">
+        <v>3.2000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A99" t="s">
+        <v>107</v>
+      </c>
+      <c r="B99" s="21">
+        <v>3.2000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A100" t="s">
+        <v>108</v>
+      </c>
+      <c r="B100" s="21">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A101" t="s">
+        <v>39</v>
+      </c>
+      <c r="B101" s="21">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A102" t="s">
+        <v>109</v>
+      </c>
+      <c r="B102" s="21">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A103" t="s">
+        <v>110</v>
+      </c>
+      <c r="B103" s="21">
+        <v>2.8E-3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A104" t="s">
+        <v>111</v>
+      </c>
+      <c r="B104" s="21">
+        <v>2.7000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A105" t="s">
+        <v>112</v>
+      </c>
+      <c r="B105" s="21">
+        <v>2.7000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A106" t="s">
+        <v>40</v>
+      </c>
+      <c r="B106" s="21">
+        <v>2.3999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A107" t="s">
+        <v>113</v>
+      </c>
+      <c r="B107" s="21">
+        <v>2.3E-3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A108" t="s">
+        <v>114</v>
+      </c>
+      <c r="B108" s="21">
+        <v>2.2000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A109" t="s">
+        <v>115</v>
+      </c>
+      <c r="B109" s="21">
+        <v>2.2000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A110" t="s">
+        <v>116</v>
+      </c>
+      <c r="B110" s="21">
+        <v>2.2000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A111" t="s">
+        <v>117</v>
+      </c>
+      <c r="B111" s="21">
+        <v>1.6000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A112" t="s">
+        <v>118</v>
+      </c>
+      <c r="B112" s="21">
+        <v>1.6000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A113" t="s">
+        <v>119</v>
+      </c>
+      <c r="B113" s="21">
+        <v>1.5E-3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A114" t="s">
+        <v>120</v>
+      </c>
+      <c r="B114" s="21">
+        <v>1.5E-3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A115" t="s">
+        <v>121</v>
+      </c>
+      <c r="B115" s="21">
+        <v>1.4E-3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A116" t="s">
+        <v>122</v>
+      </c>
+      <c r="B116" s="21">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A117" t="s">
+        <v>123</v>
+      </c>
+      <c r="B117" s="21">
+        <v>8.9999999999999998E-4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A118" t="s">
+        <v>124</v>
+      </c>
+      <c r="B118" s="21">
+        <v>6.9999999999999999E-4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A119" t="s">
+        <v>44</v>
+      </c>
+      <c r="B119" s="21">
+        <v>4.0000000000000002E-4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A120" t="s">
+        <v>125</v>
+      </c>
+      <c r="B120" s="21">
+        <v>2.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A121" t="s">
+        <v>126</v>
+      </c>
+      <c r="B121" s="21">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A122" t="s">
+        <v>127</v>
+      </c>
+      <c r="B122" s="21">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A123" t="s">
+        <v>128</v>
+      </c>
+      <c r="B123" s="21">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A124" t="s">
+        <v>129</v>
+      </c>
+      <c r="B124" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A125" t="s">
+        <v>130</v>
+      </c>
+      <c r="B125" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A126" t="s">
+        <v>131</v>
+      </c>
+      <c r="B126" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A127" t="s">
+        <v>132</v>
+      </c>
+      <c r="B127" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A128" t="s">
+        <v>133</v>
+      </c>
+      <c r="B128" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A129" t="s">
+        <v>134</v>
+      </c>
+      <c r="B129" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A130" t="s">
+        <v>135</v>
+      </c>
+      <c r="B130" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A131" t="s">
+        <v>38</v>
+      </c>
+      <c r="B131" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A132" t="s">
+        <v>136</v>
+      </c>
+      <c r="B132" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A133" t="s">
+        <v>137</v>
+      </c>
+      <c r="B133" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A134" t="s">
+        <v>138</v>
+      </c>
+      <c r="B134" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A135" t="s">
+        <v>139</v>
+      </c>
+      <c r="B135" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A136" t="s">
+        <v>140</v>
+      </c>
+      <c r="B136" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A137" t="s">
+        <v>141</v>
+      </c>
+      <c r="B137" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A138" t="s">
+        <v>142</v>
+      </c>
+      <c r="B138" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A139" t="s">
+        <v>143</v>
+      </c>
+      <c r="B139" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A140" t="s">
+        <v>144</v>
+      </c>
+      <c r="B140" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A141" t="s">
+        <v>145</v>
+      </c>
+      <c r="B141" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A142" t="s">
+        <v>146</v>
+      </c>
+      <c r="B142" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A143" t="s">
+        <v>147</v>
+      </c>
+      <c r="B143" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A144" t="s">
+        <v>148</v>
+      </c>
+      <c r="B144" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A145" t="s">
+        <v>45</v>
+      </c>
+      <c r="B145" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A146" t="s">
+        <v>149</v>
+      </c>
+      <c r="B146" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A147" t="s">
+        <v>46</v>
+      </c>
+      <c r="B147" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A148" t="s">
+        <v>150</v>
+      </c>
+      <c r="B148" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A149" t="s">
+        <v>41</v>
+      </c>
+      <c r="B149" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A150" t="s">
+        <v>151</v>
+      </c>
+      <c r="B150" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A151" t="s">
+        <v>152</v>
+      </c>
+      <c r="B151" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A152" t="s">
+        <v>43</v>
+      </c>
+      <c r="B152" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A153" t="s">
+        <v>153</v>
+      </c>
+      <c r="B153" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A154" t="s">
+        <v>154</v>
+      </c>
+      <c r="B154" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A155" t="s">
+        <v>155</v>
+      </c>
+      <c r="B155" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A156" t="s">
+        <v>156</v>
+      </c>
+      <c r="B156" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A157" t="s">
+        <v>157</v>
+      </c>
+      <c r="B157" s="21">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39E9B7EE-902D-4E4B-B04D-1334FB1D74B9}">
+  <dimension ref="A2:F157"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="39.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="21">
+        <v>9.5200000000000007E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="21">
+        <v>2.7099999999999999E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="21">
+        <v>6.2700000000000006E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="21">
+        <v>2.0199999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="21">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" s="21">
+        <v>6.1999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" s="21">
+        <v>2.2000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="22">
+        <v>1.9699999999999999E-2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="21">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>139</v>
+      </c>
+      <c r="B10" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="21">
+        <v>2.3599999999999999E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="21">
+        <v>3.2000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>140</v>
+      </c>
+      <c r="B13" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" s="21">
+        <v>2.2000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="22">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A16" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="22">
+        <v>1.2200000000000001E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="21">
+        <v>3.0499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="21">
+        <v>4.1399999999999999E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="22">
+        <v>1.47E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>146</v>
+      </c>
+      <c r="B21" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" s="21">
+        <v>6.7000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" s="21">
+        <v>3.8999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>156</v>
+      </c>
+      <c r="B24" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>129</v>
+      </c>
+      <c r="B25" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>155</v>
+      </c>
+      <c r="B26" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>128</v>
+      </c>
+      <c r="B27" s="21">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="21">
+        <v>7.3000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A29" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="22">
+        <v>1.47E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="21">
+        <v>5.4999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="21">
+        <v>5.4999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="21">
+        <v>4.65E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" s="21">
+        <v>3.6200000000000003E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="21">
+        <v>4.2599999999999999E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36" s="21">
+        <v>5.1000000000000004E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="21">
+        <v>4.0000000000000002E-4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>19</v>
+      </c>
+      <c r="B39" s="21">
+        <v>3.2000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40" s="21">
+        <v>3.1E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="21">
+        <v>2.3999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>105</v>
+      </c>
+      <c r="B42" s="21">
+        <v>3.3E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>79</v>
+      </c>
+      <c r="B43" s="21">
+        <v>8.8999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>152</v>
+      </c>
+      <c r="B44" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>151</v>
+      </c>
+      <c r="B45" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>100</v>
+      </c>
+      <c r="B46" s="21">
+        <v>4.3E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>102</v>
+      </c>
+      <c r="B47" s="21">
+        <v>3.8999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>109</v>
+      </c>
+      <c r="B48" s="21">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>154</v>
+      </c>
+      <c r="B49" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>153</v>
+      </c>
+      <c r="B50" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A51" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B51" s="22">
+        <v>1.66E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>4</v>
+      </c>
+      <c r="B52" s="21">
+        <v>6.6699999999999995E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>12</v>
+      </c>
+      <c r="B53" s="21">
+        <v>2.06E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>22</v>
+      </c>
+      <c r="B54" s="21">
+        <v>1.8499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>120</v>
+      </c>
+      <c r="B55" s="21">
+        <v>1.5E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A56" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B56" s="22">
+        <v>1.11E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A57" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B57" s="22">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>149</v>
+      </c>
+      <c r="B58" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A59" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B59" s="22">
+        <v>1.26E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A60" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B60" s="22">
+        <v>1.03E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>99</v>
+      </c>
+      <c r="B61" s="21">
+        <v>4.5999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A62" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B62" s="22">
+        <v>1.5800000000000002E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>127</v>
+      </c>
+      <c r="B63" s="21">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>92</v>
+      </c>
+      <c r="B64" s="21">
+        <v>6.1999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>24</v>
+      </c>
+      <c r="B65" s="21">
+        <v>2.0400000000000001E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>25</v>
+      </c>
+      <c r="B66" s="21">
+        <v>2.12E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>137</v>
+      </c>
+      <c r="B67" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>94</v>
+      </c>
+      <c r="B68" s="21">
+        <v>5.5999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A69" t="s">
+        <v>103</v>
+      </c>
+      <c r="B69" s="21">
+        <v>3.8E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>85</v>
+      </c>
+      <c r="B70" s="21">
+        <v>8.0999999999999996E-3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>144</v>
+      </c>
+      <c r="B71" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A72" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B72" s="22">
+        <v>1.3299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>131</v>
+      </c>
+      <c r="B73" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>82</v>
+      </c>
+      <c r="B74" s="21">
+        <v>8.5000000000000006E-3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
+        <v>75</v>
+      </c>
+      <c r="B75" s="21">
+        <v>9.7000000000000003E-3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A76" t="s">
+        <v>124</v>
+      </c>
+      <c r="B76" s="21">
+        <v>6.9999999999999999E-4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A77" t="s">
+        <v>32</v>
+      </c>
+      <c r="B77" s="21">
+        <v>1.17E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A78" t="s">
+        <v>30</v>
+      </c>
+      <c r="B78" s="21">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A79" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B79" s="22">
+        <v>1.7299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A80" t="s">
+        <v>126</v>
+      </c>
+      <c r="B80" s="21">
+        <v>1E-4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A81" t="s">
+        <v>107</v>
+      </c>
+      <c r="B81" s="21">
+        <v>3.2000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A82" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B82" s="22">
+        <v>1.46E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A83" t="s">
+        <v>111</v>
+      </c>
+      <c r="B83" s="21">
+        <v>2.7000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A84" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B84" s="22">
+        <v>1.14E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A85" t="s">
+        <v>142</v>
+      </c>
+      <c r="B85" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A86" t="s">
+        <v>125</v>
+      </c>
+      <c r="B86" s="21">
+        <v>2.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A87" t="s">
+        <v>110</v>
+      </c>
+      <c r="B87" s="21">
+        <v>2.8E-3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A88" t="s">
+        <v>74</v>
+      </c>
+      <c r="B88" s="21">
+        <v>9.7000000000000003E-3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A89" t="s">
+        <v>28</v>
+      </c>
+      <c r="B89" s="21">
+        <v>7.6E-3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A90" t="s">
+        <v>37</v>
+      </c>
+      <c r="B90" s="21">
+        <v>1.5699999999999999E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A91" t="s">
+        <v>10</v>
+      </c>
+      <c r="B91" s="21">
+        <v>5.1900000000000002E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A92" t="s">
+        <v>42</v>
+      </c>
+      <c r="B92" s="21">
+        <v>2.0500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A93" t="s">
+        <v>43</v>
+      </c>
+      <c r="B93" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A94" t="s">
+        <v>27</v>
+      </c>
+      <c r="B94" s="21">
+        <v>6.8999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A95" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B95" s="22">
+        <v>1.0800000000000001E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A96" t="s">
+        <v>134</v>
+      </c>
+      <c r="B96" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A97" t="s">
+        <v>116</v>
+      </c>
+      <c r="B97" s="21">
+        <v>2.2000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A98" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B98" s="22">
+        <v>1.0800000000000001E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A99" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B99" s="22">
+        <v>2.2800000000000001E-2</v>
+      </c>
+      <c r="C99" t="s">
+        <v>27</v>
+      </c>
+      <c r="D99" s="21">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="E99" t="s">
+        <v>25</v>
+      </c>
+      <c r="F99" s="21">
+        <v>2.12E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A100" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B100" s="22">
+        <v>1.21E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A101" t="s">
+        <v>117</v>
+      </c>
+      <c r="B101" s="21">
+        <v>1.6000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A102" t="s">
+        <v>133</v>
+      </c>
+      <c r="B102" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A103" t="s">
+        <v>112</v>
+      </c>
+      <c r="B103" s="21">
+        <v>2.7000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A104" t="s">
+        <v>80</v>
+      </c>
+      <c r="B104" s="21">
+        <v>8.8000000000000005E-3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A105" t="s">
+        <v>23</v>
+      </c>
+      <c r="B105" s="21">
+        <v>1.2800000000000001E-2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A106" t="s">
+        <v>31</v>
+      </c>
+      <c r="B106" s="21">
+        <v>8.2000000000000007E-3</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A107" t="s">
+        <v>84</v>
+      </c>
+      <c r="B107" s="21">
+        <v>8.3000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A108" t="s">
+        <v>141</v>
+      </c>
+      <c r="B108" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A109" t="s">
+        <v>104</v>
+      </c>
+      <c r="B109" s="21">
+        <v>3.5000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A110" t="s">
+        <v>95</v>
+      </c>
+      <c r="B110" s="21">
+        <v>5.4999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A111" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B111" s="22">
+        <v>1.0500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A112" t="s">
+        <v>136</v>
+      </c>
+      <c r="B112" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A113" t="s">
+        <v>138</v>
+      </c>
+      <c r="B113" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A114" t="s">
+        <v>143</v>
+      </c>
+      <c r="B114" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A115" t="s">
+        <v>150</v>
+      </c>
+      <c r="B115" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A116" t="s">
+        <v>157</v>
+      </c>
+      <c r="B116" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A117" t="s">
+        <v>39</v>
+      </c>
+      <c r="B117" s="21">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A118" t="s">
+        <v>13</v>
+      </c>
+      <c r="B118" s="21">
+        <v>4.2200000000000001E-2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A119" t="s">
+        <v>38</v>
+      </c>
+      <c r="B119" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A120" t="s">
+        <v>97</v>
+      </c>
+      <c r="B120" s="21">
+        <v>4.8999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A121" t="s">
+        <v>122</v>
+      </c>
+      <c r="B121" s="21">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A122" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B122" s="22">
+        <v>1.5699999999999999E-2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A123" t="s">
+        <v>78</v>
+      </c>
+      <c r="B123" s="21">
+        <v>9.4000000000000004E-3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A124" t="s">
+        <v>76</v>
+      </c>
+      <c r="B124" s="21">
+        <v>9.5999999999999992E-3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A125" t="s">
+        <v>130</v>
+      </c>
+      <c r="B125" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A126" t="s">
+        <v>81</v>
+      </c>
+      <c r="B126" s="21">
+        <v>8.5000000000000006E-3</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A127" t="s">
+        <v>90</v>
+      </c>
+      <c r="B127" s="21">
+        <v>6.3E-3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A128" t="s">
+        <v>119</v>
+      </c>
+      <c r="B128" s="21">
+        <v>1.5E-3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A129" t="s">
+        <v>113</v>
+      </c>
+      <c r="B129" s="21">
+        <v>2.3E-3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A130" t="s">
+        <v>36</v>
+      </c>
+      <c r="B130" s="21">
+        <v>7.6E-3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" s="21">
+        <v>3.6299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A132" t="s">
+        <v>35</v>
+      </c>
+      <c r="B132" s="21">
+        <v>4.8999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A133" t="s">
+        <v>145</v>
+      </c>
+      <c r="B133" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A134" t="s">
+        <v>93</v>
+      </c>
+      <c r="B134" s="21">
+        <v>5.7999999999999996E-3</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A135" t="s">
+        <v>132</v>
+      </c>
+      <c r="B135" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A136" t="s">
+        <v>98</v>
+      </c>
+      <c r="B136" s="21">
+        <v>4.7999999999999996E-3</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A137" t="s">
+        <v>123</v>
+      </c>
+      <c r="B137" s="21">
+        <v>8.9999999999999998E-4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A138" t="s">
+        <v>147</v>
+      </c>
+      <c r="B138" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A139" t="s">
+        <v>77</v>
+      </c>
+      <c r="B139" s="21">
+        <v>9.4000000000000004E-3</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A140" t="s">
+        <v>148</v>
+      </c>
+      <c r="B140" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A141" t="s">
+        <v>135</v>
+      </c>
+      <c r="B141" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A142" t="s">
+        <v>108</v>
+      </c>
+      <c r="B142" s="21">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A143" t="s">
+        <v>6</v>
+      </c>
+      <c r="B143" s="21">
+        <v>5.9900000000000002E-2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A144" t="s">
+        <v>20</v>
+      </c>
+      <c r="B144" s="21">
+        <v>3.3799999999999997E-2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A145" t="s">
+        <v>21</v>
+      </c>
+      <c r="B145" s="21">
+        <v>1.77E-2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A146" t="s">
+        <v>62</v>
+      </c>
+      <c r="B146" s="21">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A147" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B147" s="22">
+        <v>1.7100000000000001E-2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A148" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B148" s="22">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A149" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B149" s="22">
+        <v>2.7799999999999998E-2</v>
+      </c>
+      <c r="C149" t="s">
+        <v>21</v>
+      </c>
+      <c r="D149" s="21">
+        <v>1.77E-2</v>
+      </c>
+      <c r="E149" t="s">
+        <v>22</v>
+      </c>
+      <c r="F149" s="21">
+        <v>1.8499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A150" t="s">
+        <v>121</v>
+      </c>
+      <c r="B150" s="21">
+        <v>1.4E-3</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A151" t="s">
+        <v>83</v>
+      </c>
+      <c r="B151" s="21">
+        <v>8.3000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A152" t="s">
+        <v>87</v>
+      </c>
+      <c r="B152" s="21">
+        <v>7.7000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A153" t="s">
+        <v>96</v>
+      </c>
+      <c r="B153" s="21">
+        <v>5.1999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A154" t="s">
+        <v>118</v>
+      </c>
+      <c r="B154" s="21">
+        <v>1.6000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A155" t="s">
+        <v>86</v>
+      </c>
+      <c r="B155" s="21">
+        <v>7.7999999999999996E-3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A156" t="s">
+        <v>3</v>
+      </c>
+      <c r="B156" s="21">
+        <v>7.7899999999999997E-2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A157" t="s">
+        <v>8</v>
+      </c>
+      <c r="B157" s="21">
+        <v>4.3400000000000001E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F157">
+    <sortCondition ref="A2:A157"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/mutual information after cleaning.xlsx
+++ b/docs/mutual information after cleaning.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kushn\projects\kaggle\Telco customer churn 11.1.3\telco-customer-churn\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B5E9202-2AB0-4E7B-82EC-9438244EE19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342FDE16-467D-4F92-AA9D-7222A4C0B9DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14685" yWindow="2385" windowWidth="13650" windowHeight="15345" activeTab="2" xr2:uid="{EF238555-2496-4093-8BBF-7018B023DB21}"/>
+    <workbookView xWindow="-14685" yWindow="2385" windowWidth="13650" windowHeight="15345" activeTab="1" xr2:uid="{EF238555-2496-4093-8BBF-7018B023DB21}"/>
     <workbookView xWindow="-28920" yWindow="1710" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{99A4C60C-90BA-48B8-87B6-754AB4E2835B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="experiment 2" sheetId="1" r:id="rId1"/>
+    <sheet name="experiment 3" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="158">
   <si>
     <t>Feature</t>
   </si>
@@ -3303,1299 +3302,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39E9B7EE-902D-4E4B-B04D-1334FB1D74B9}">
-  <dimension ref="A2:F157"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="39.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.265625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="21">
-        <v>9.5200000000000007E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="21">
-        <v>2.7099999999999999E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="21">
-        <v>6.2700000000000006E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="21">
-        <v>2.0199999999999999E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="21">
-        <v>1.4E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B7" s="21">
-        <v>6.1999999999999998E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>115</v>
-      </c>
-      <c r="B8" s="21">
-        <v>2.2000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="22">
-        <v>1.9699999999999999E-2</v>
-      </c>
-      <c r="C9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="21">
-        <v>1.4E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>139</v>
-      </c>
-      <c r="B10" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="21">
-        <v>2.3599999999999999E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B12" s="21">
-        <v>3.2000000000000002E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>140</v>
-      </c>
-      <c r="B13" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>114</v>
-      </c>
-      <c r="B14" s="21">
-        <v>2.2000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A15" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15" s="22">
-        <v>1.0999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A16" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" s="22">
-        <v>1.2200000000000001E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" s="21">
-        <v>3.0499999999999999E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="21">
-        <v>4.1399999999999999E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A20" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" s="22">
-        <v>1.47E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>146</v>
-      </c>
-      <c r="B21" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>89</v>
-      </c>
-      <c r="B22" s="21">
-        <v>6.7000000000000002E-3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>101</v>
-      </c>
-      <c r="B23" s="21">
-        <v>3.8999999999999998E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>156</v>
-      </c>
-      <c r="B24" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>129</v>
-      </c>
-      <c r="B25" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>155</v>
-      </c>
-      <c r="B26" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>128</v>
-      </c>
-      <c r="B27" s="21">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>88</v>
-      </c>
-      <c r="B28" s="21">
-        <v>7.3000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A29" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B29" s="22">
-        <v>1.47E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>47</v>
-      </c>
-      <c r="B30" s="21">
-        <v>5.4999999999999997E-3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>46</v>
-      </c>
-      <c r="B31" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
-        <v>34</v>
-      </c>
-      <c r="B32" s="21">
-        <v>5.4999999999999997E-3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33" s="21">
-        <v>4.65E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>16</v>
-      </c>
-      <c r="B34" s="21">
-        <v>3.6200000000000003E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
-        <v>9</v>
-      </c>
-      <c r="B35" s="21">
-        <v>4.2599999999999999E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>33</v>
-      </c>
-      <c r="B36" s="21">
-        <v>5.1000000000000004E-3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="21">
-        <v>4.0000000000000002E-4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A39" t="s">
-        <v>19</v>
-      </c>
-      <c r="B39" s="21">
-        <v>3.2000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A40" t="s">
-        <v>14</v>
-      </c>
-      <c r="B40" s="21">
-        <v>3.1E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A41" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="21">
-        <v>2.3999999999999998E-3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A42" t="s">
-        <v>105</v>
-      </c>
-      <c r="B42" s="21">
-        <v>3.3E-3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A43" t="s">
-        <v>79</v>
-      </c>
-      <c r="B43" s="21">
-        <v>8.8999999999999999E-3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A44" t="s">
-        <v>152</v>
-      </c>
-      <c r="B44" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A45" t="s">
-        <v>151</v>
-      </c>
-      <c r="B45" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A46" t="s">
-        <v>100</v>
-      </c>
-      <c r="B46" s="21">
-        <v>4.3E-3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A47" t="s">
-        <v>102</v>
-      </c>
-      <c r="B47" s="21">
-        <v>3.8999999999999998E-3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A48" t="s">
-        <v>109</v>
-      </c>
-      <c r="B48" s="21">
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A49" t="s">
-        <v>154</v>
-      </c>
-      <c r="B49" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A50" t="s">
-        <v>153</v>
-      </c>
-      <c r="B50" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A51" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B51" s="22">
-        <v>1.66E-2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A52" t="s">
-        <v>4</v>
-      </c>
-      <c r="B52" s="21">
-        <v>6.6699999999999995E-2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A53" t="s">
-        <v>12</v>
-      </c>
-      <c r="B53" s="21">
-        <v>2.06E-2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A54" t="s">
-        <v>22</v>
-      </c>
-      <c r="B54" s="21">
-        <v>1.8499999999999999E-2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A55" t="s">
-        <v>120</v>
-      </c>
-      <c r="B55" s="21">
-        <v>1.5E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A56" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B56" s="22">
-        <v>1.11E-2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A57" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B57" s="22">
-        <v>1.4E-2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A58" t="s">
-        <v>149</v>
-      </c>
-      <c r="B58" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A59" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B59" s="22">
-        <v>1.26E-2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A60" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B60" s="22">
-        <v>1.03E-2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A61" t="s">
-        <v>99</v>
-      </c>
-      <c r="B61" s="21">
-        <v>4.5999999999999999E-3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A62" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B62" s="22">
-        <v>1.5800000000000002E-2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A63" t="s">
-        <v>127</v>
-      </c>
-      <c r="B63" s="21">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A64" t="s">
-        <v>92</v>
-      </c>
-      <c r="B64" s="21">
-        <v>6.1999999999999998E-3</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A65" t="s">
-        <v>24</v>
-      </c>
-      <c r="B65" s="21">
-        <v>2.0400000000000001E-2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A66" t="s">
-        <v>25</v>
-      </c>
-      <c r="B66" s="21">
-        <v>2.12E-2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A67" t="s">
-        <v>137</v>
-      </c>
-      <c r="B67" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A68" t="s">
-        <v>94</v>
-      </c>
-      <c r="B68" s="21">
-        <v>5.5999999999999999E-3</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A69" t="s">
-        <v>103</v>
-      </c>
-      <c r="B69" s="21">
-        <v>3.8E-3</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A70" t="s">
-        <v>85</v>
-      </c>
-      <c r="B70" s="21">
-        <v>8.0999999999999996E-3</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A71" t="s">
-        <v>144</v>
-      </c>
-      <c r="B71" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A72" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B72" s="22">
-        <v>1.3299999999999999E-2</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A73" t="s">
-        <v>131</v>
-      </c>
-      <c r="B73" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A74" t="s">
-        <v>82</v>
-      </c>
-      <c r="B74" s="21">
-        <v>8.5000000000000006E-3</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A75" t="s">
-        <v>75</v>
-      </c>
-      <c r="B75" s="21">
-        <v>9.7000000000000003E-3</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A76" t="s">
-        <v>124</v>
-      </c>
-      <c r="B76" s="21">
-        <v>6.9999999999999999E-4</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A77" t="s">
-        <v>32</v>
-      </c>
-      <c r="B77" s="21">
-        <v>1.17E-2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A78" t="s">
-        <v>30</v>
-      </c>
-      <c r="B78" s="21">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A79" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B79" s="22">
-        <v>1.7299999999999999E-2</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A80" t="s">
-        <v>126</v>
-      </c>
-      <c r="B80" s="21">
-        <v>1E-4</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A81" t="s">
-        <v>107</v>
-      </c>
-      <c r="B81" s="21">
-        <v>3.2000000000000002E-3</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A82" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B82" s="22">
-        <v>1.46E-2</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A83" t="s">
-        <v>111</v>
-      </c>
-      <c r="B83" s="21">
-        <v>2.7000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A84" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B84" s="22">
-        <v>1.14E-2</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A85" t="s">
-        <v>142</v>
-      </c>
-      <c r="B85" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A86" t="s">
-        <v>125</v>
-      </c>
-      <c r="B86" s="21">
-        <v>2.0000000000000001E-4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A87" t="s">
-        <v>110</v>
-      </c>
-      <c r="B87" s="21">
-        <v>2.8E-3</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A88" t="s">
-        <v>74</v>
-      </c>
-      <c r="B88" s="21">
-        <v>9.7000000000000003E-3</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A89" t="s">
-        <v>28</v>
-      </c>
-      <c r="B89" s="21">
-        <v>7.6E-3</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A90" t="s">
-        <v>37</v>
-      </c>
-      <c r="B90" s="21">
-        <v>1.5699999999999999E-2</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A91" t="s">
-        <v>10</v>
-      </c>
-      <c r="B91" s="21">
-        <v>5.1900000000000002E-2</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A92" t="s">
-        <v>42</v>
-      </c>
-      <c r="B92" s="21">
-        <v>2.0500000000000001E-2</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A93" t="s">
-        <v>43</v>
-      </c>
-      <c r="B93" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A94" t="s">
-        <v>27</v>
-      </c>
-      <c r="B94" s="21">
-        <v>6.8999999999999999E-3</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A95" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B95" s="22">
-        <v>1.0800000000000001E-2</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A96" t="s">
-        <v>134</v>
-      </c>
-      <c r="B96" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A97" t="s">
-        <v>116</v>
-      </c>
-      <c r="B97" s="21">
-        <v>2.2000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A98" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B98" s="22">
-        <v>1.0800000000000001E-2</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A99" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B99" s="22">
-        <v>2.2800000000000001E-2</v>
-      </c>
-      <c r="C99" t="s">
-        <v>27</v>
-      </c>
-      <c r="D99" s="21">
-        <v>6.8999999999999999E-3</v>
-      </c>
-      <c r="E99" t="s">
-        <v>25</v>
-      </c>
-      <c r="F99" s="21">
-        <v>2.12E-2</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A100" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B100" s="22">
-        <v>1.21E-2</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A101" t="s">
-        <v>117</v>
-      </c>
-      <c r="B101" s="21">
-        <v>1.6000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A102" t="s">
-        <v>133</v>
-      </c>
-      <c r="B102" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A103" t="s">
-        <v>112</v>
-      </c>
-      <c r="B103" s="21">
-        <v>2.7000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A104" t="s">
-        <v>80</v>
-      </c>
-      <c r="B104" s="21">
-        <v>8.8000000000000005E-3</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A105" t="s">
-        <v>23</v>
-      </c>
-      <c r="B105" s="21">
-        <v>1.2800000000000001E-2</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A106" t="s">
-        <v>31</v>
-      </c>
-      <c r="B106" s="21">
-        <v>8.2000000000000007E-3</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A107" t="s">
-        <v>84</v>
-      </c>
-      <c r="B107" s="21">
-        <v>8.3000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A108" t="s">
-        <v>141</v>
-      </c>
-      <c r="B108" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A109" t="s">
-        <v>104</v>
-      </c>
-      <c r="B109" s="21">
-        <v>3.5000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A110" t="s">
-        <v>95</v>
-      </c>
-      <c r="B110" s="21">
-        <v>5.4999999999999997E-3</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A111" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B111" s="22">
-        <v>1.0500000000000001E-2</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A112" t="s">
-        <v>136</v>
-      </c>
-      <c r="B112" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A113" t="s">
-        <v>138</v>
-      </c>
-      <c r="B113" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A114" t="s">
-        <v>143</v>
-      </c>
-      <c r="B114" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A115" t="s">
-        <v>150</v>
-      </c>
-      <c r="B115" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A116" t="s">
-        <v>157</v>
-      </c>
-      <c r="B116" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A117" t="s">
-        <v>39</v>
-      </c>
-      <c r="B117" s="21">
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A118" t="s">
-        <v>13</v>
-      </c>
-      <c r="B118" s="21">
-        <v>4.2200000000000001E-2</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A119" t="s">
-        <v>38</v>
-      </c>
-      <c r="B119" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A120" t="s">
-        <v>97</v>
-      </c>
-      <c r="B120" s="21">
-        <v>4.8999999999999998E-3</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A121" t="s">
-        <v>122</v>
-      </c>
-      <c r="B121" s="21">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A122" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B122" s="22">
-        <v>1.5699999999999999E-2</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A123" t="s">
-        <v>78</v>
-      </c>
-      <c r="B123" s="21">
-        <v>9.4000000000000004E-3</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A124" t="s">
-        <v>76</v>
-      </c>
-      <c r="B124" s="21">
-        <v>9.5999999999999992E-3</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A125" t="s">
-        <v>130</v>
-      </c>
-      <c r="B125" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A126" t="s">
-        <v>81</v>
-      </c>
-      <c r="B126" s="21">
-        <v>8.5000000000000006E-3</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A127" t="s">
-        <v>90</v>
-      </c>
-      <c r="B127" s="21">
-        <v>6.3E-3</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A128" t="s">
-        <v>119</v>
-      </c>
-      <c r="B128" s="21">
-        <v>1.5E-3</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A129" t="s">
-        <v>113</v>
-      </c>
-      <c r="B129" s="21">
-        <v>2.3E-3</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A130" t="s">
-        <v>36</v>
-      </c>
-      <c r="B130" s="21">
-        <v>7.6E-3</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" s="21">
-        <v>3.6299999999999999E-2</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A132" t="s">
-        <v>35</v>
-      </c>
-      <c r="B132" s="21">
-        <v>4.8999999999999998E-3</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A133" t="s">
-        <v>145</v>
-      </c>
-      <c r="B133" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A134" t="s">
-        <v>93</v>
-      </c>
-      <c r="B134" s="21">
-        <v>5.7999999999999996E-3</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A135" t="s">
-        <v>132</v>
-      </c>
-      <c r="B135" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A136" t="s">
-        <v>98</v>
-      </c>
-      <c r="B136" s="21">
-        <v>4.7999999999999996E-3</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A137" t="s">
-        <v>123</v>
-      </c>
-      <c r="B137" s="21">
-        <v>8.9999999999999998E-4</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A138" t="s">
-        <v>147</v>
-      </c>
-      <c r="B138" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A139" t="s">
-        <v>77</v>
-      </c>
-      <c r="B139" s="21">
-        <v>9.4000000000000004E-3</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A140" t="s">
-        <v>148</v>
-      </c>
-      <c r="B140" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A141" t="s">
-        <v>135</v>
-      </c>
-      <c r="B141" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A142" t="s">
-        <v>108</v>
-      </c>
-      <c r="B142" s="21">
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A143" t="s">
-        <v>6</v>
-      </c>
-      <c r="B143" s="21">
-        <v>5.9900000000000002E-2</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A144" t="s">
-        <v>20</v>
-      </c>
-      <c r="B144" s="21">
-        <v>3.3799999999999997E-2</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A145" t="s">
-        <v>21</v>
-      </c>
-      <c r="B145" s="21">
-        <v>1.77E-2</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A146" t="s">
-        <v>62</v>
-      </c>
-      <c r="B146" s="21">
-        <v>1.2999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A147" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B147" s="22">
-        <v>1.7100000000000001E-2</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A148" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B148" s="22">
-        <v>1.2999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A149" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B149" s="22">
-        <v>2.7799999999999998E-2</v>
-      </c>
-      <c r="C149" t="s">
-        <v>21</v>
-      </c>
-      <c r="D149" s="21">
-        <v>1.77E-2</v>
-      </c>
-      <c r="E149" t="s">
-        <v>22</v>
-      </c>
-      <c r="F149" s="21">
-        <v>1.8499999999999999E-2</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A150" t="s">
-        <v>121</v>
-      </c>
-      <c r="B150" s="21">
-        <v>1.4E-3</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A151" t="s">
-        <v>83</v>
-      </c>
-      <c r="B151" s="21">
-        <v>8.3000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A152" t="s">
-        <v>87</v>
-      </c>
-      <c r="B152" s="21">
-        <v>7.7000000000000002E-3</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A153" t="s">
-        <v>96</v>
-      </c>
-      <c r="B153" s="21">
-        <v>5.1999999999999998E-3</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A154" t="s">
-        <v>118</v>
-      </c>
-      <c r="B154" s="21">
-        <v>1.6000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A155" t="s">
-        <v>86</v>
-      </c>
-      <c r="B155" s="21">
-        <v>7.7999999999999996E-3</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A156" t="s">
-        <v>3</v>
-      </c>
-      <c r="B156" s="21">
-        <v>7.7899999999999997E-2</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A157" t="s">
-        <v>8</v>
-      </c>
-      <c r="B157" s="21">
-        <v>4.3400000000000001E-2</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F157">
-    <sortCondition ref="A2:A157"/>
-  </sortState>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>